--- a/orcamentos_gerados/Orcamento_Luciano.xlsx
+++ b/orcamentos_gerados/Orcamento_Luciano.xlsx
@@ -4123,7 +4123,9 @@
           <t>CARRETA 1</t>
         </is>
       </c>
-      <c r="K7" s="313" t="n"/>
+      <c r="K7" s="313" t="n">
+        <v>2000</v>
+      </c>
       <c r="L7" s="20" t="n"/>
       <c r="M7" s="18" t="n"/>
       <c r="N7" s="3" t="n"/>
@@ -4277,7 +4279,9 @@
           <t>CARRETA 2</t>
         </is>
       </c>
-      <c r="K8" s="314" t="n"/>
+      <c r="K8" s="314" t="n">
+        <v>750</v>
+      </c>
       <c r="L8" s="20" t="n"/>
       <c r="M8" s="21" t="inlineStr">
         <is>
@@ -4447,7 +4451,9 @@
           <t>CARRETA 3</t>
         </is>
       </c>
-      <c r="K9" s="318" t="n"/>
+      <c r="K9" s="318" t="n">
+        <v>860</v>
+      </c>
       <c r="L9" s="319" t="n"/>
       <c r="M9" s="319">
         <f>SUM(K7:K12)</f>
@@ -6737,7 +6743,11 @@
       </c>
       <c r="F23" s="342" t="n"/>
       <c r="G23" s="343" t="n"/>
-      <c r="H23" s="359" t="n"/>
+      <c r="H23" s="359" t="inlineStr">
+        <is>
+          <t>27 dias</t>
+        </is>
+      </c>
       <c r="I23" s="326" t="n"/>
       <c r="K23" s="195" t="n"/>
       <c r="L23" s="303" t="n"/>
